--- a/abdm-ft/archive/final-20261029-before-share-rerun/M2_BUILDING_HIP_TEST_CASES.xlsx
+++ b/abdm-ft/archive/final-20261029-before-share-rerun/M2_BUILDING_HIP_TEST_CASES.xlsx
@@ -1553,7 +1553,7 @@
       <c r="J19" s="14" t="n"/>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>Inbound POST /api/v3/hip/patient/care-context/discover REQUEST-ID 17df06aa-b95d-4f33-b2d0-5ba9cbf0677b at 23:24:10 IST: transactionId f3c99f71-3824-4f30-8a2b-afc473b1f443 present, patient.id present, patient.verifiedIdentifiers [MOBILE, ABHA_NUMBER, abhaAddress], gender F, yearOfBirth 2004</t>
+          <t>Inbound POST /api/v3/hip/patient/care-context/discover REQUEST-ID 17df06aa-b95d-4f33-b2d0-5ba9cbf0677b at 23:24:10 IST: transactionId f3c99f71-3824-4f30-8a2b-afc473b1f443 present, patient.id present, patient.verifiedIdentifiers [MOBILE, ABHA_NUMBER, abhaAddress], gender F, yearOfBirth [masked]</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
@@ -1610,7 +1610,7 @@
       <c r="J20" s="16" t="n"/>
       <c r="K20" s="16" t="inlineStr">
         <is>
-          <t>Matched by MOBILE to patient OCM123-2026-0013 (registered without ABHA; Female, born 2004, mobile ending 5506); on-discover sent with matchedBy [MOBILE] and patient[].careContexts [RX-67209C38-D094-4EB0-B928-A13D4529CF57], accepted by ABDM; the PHR app showed that record under our patient reference (USER_INIT_LINK_604/phr-1.png)</t>
+          <t>Matched by MOBILE to patient OCM123-2026-0013 (registered without ABHA; Female, born [masked], mobile ending 5506); on-discover sent with matchedBy [MOBILE] and patient[].careContexts [RX-67209C38-D094-4EB0-B928-A13D4529CF57], accepted by ABDM; the PHR app showed that record under our patient reference (USER_INIT_LINK_604/phr-1.png)</t>
         </is>
       </c>
       <c r="L20" s="16" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="N20" s="16" t="inlineStr">
         <is>
-          <t>Screen check: the matched patient's mobile, gender (F) and year of birth (2004) agree with the discover's. The build does not store outbound reply bodies: the on-discover content is shown by the PHR screen and by the init that selected from it.</t>
+          <t>Screen check: the matched patient's mobile, gender (F) and year of birth ([masked]) agree with the discover's. The build does not store outbound reply bodies: the on-discover content is shown by the PHR screen and by the init that selected from it.</t>
         </is>
       </c>
       <c r="O20" s="55" t="n"/>
